--- a/assets/constructions/examples/ctd_mi_cartmill1.xlsx
+++ b/assets/constructions/examples/ctd_mi_cartmill1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,11 +539,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M4000CA-SD1506</t>
+          <t>M4000CA-SN15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -570,7 +590,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>14.9</v>
+        <v>8</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="b">
@@ -593,17 +613,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>WIDIA_SD1506H</t>
+          <t>WIDIA_SN1505H</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>WID_M4000-SD1506_H</t>
+          <t>WID_M4000-SN1505_H</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>WID_123969_2945</t>
+          <t>WID_123962_2964</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -611,48 +631,46 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FC3050-TP2204-90</t>
+          <t>M4000CA-SE1504</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FP90</t>
+          <t>M4000CA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" t="n">
-        <v>30</v>
-      </c>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>11</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>TP2204W</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="b">
         <v>0</v>
       </c>
@@ -665,33 +683,43 @@
       <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>DER_FP90</t>
+          <t>WIDIA_M4000CA</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ISO_TP2204W</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+          <t>ISO_SE1504W</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>ISO_M4000-SE1504_W</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>WID_SE1504_X1</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M4000CA-HP06</t>
+          <t>M4000CA-SN12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,7 +746,7 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="b">
@@ -741,17 +769,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>WIDIA_HP06T3H</t>
+          <t>WIDIA_XSN1205H</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>WID_M4000-HP06T3_H</t>
+          <t>WID_M4000-XSN1205_H</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>WID_123954_3515</t>
+          <t>WID_123962_2907</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -759,11 +787,17 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M4000CA-XP16</t>
+          <t>M4000CA-XN15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -790,7 +824,7 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="b">
@@ -813,17 +847,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>WIDIA_XP1604H</t>
+          <t>WIDIA_XN15T6H</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>WID_M4000-XP1604_H</t>
+          <t>WID_M4000-XN15T6_H</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>WID_123930_3449</t>
+          <t>WID_VSM490_2192</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -831,11 +865,17 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M4000CA-XDPT11</t>
+          <t>M4000CA-HP06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -862,7 +902,7 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="b">
@@ -885,17 +925,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>WIDIA_XD1104H</t>
+          <t>WIDIA_HP06T3H</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>WID_M4000-XD1104_H</t>
+          <t>WID_M4000-HP06T3_H</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>WID_VSM11D_1711</t>
+          <t>WID_123954_3515</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -903,6 +943,12 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
